--- a/domain_model/Domain Model Eligibility upd.xlsx
+++ b/domain_model/Domain Model Eligibility upd.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AshishAdhikari\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\AI\phase III - new\AI-Automation-III\domain_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C46BA91-B79A-4C98-AB13-502D876ED7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C65F79-A660-4D52-8D30-C69CACECD8EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{71282556-F641-4A29-8E3B-79F171903E96}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{71282556-F641-4A29-8E3B-79F171903E96}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
   <si>
     <t>Attribute</t>
   </si>
@@ -185,9 +174,6 @@
     <t>array of string</t>
   </si>
   <si>
-    <t>List of months member was eligible (inclusive between eff. and term. date)</t>
-  </si>
-  <si>
     <t>["YYYY-MM", ...]</t>
   </si>
   <si>
@@ -206,18 +192,6 @@
     <t>true/false</t>
   </si>
   <si>
-    <t>employerGroup</t>
-  </si>
-  <si>
-    <t>array of object</t>
-  </si>
-  <si>
-    <t>Array of employer group associations</t>
-  </si>
-  <si>
-    <t>See EmployerGroupObject below</t>
-  </si>
-  <si>
     <t>coverageDesc</t>
   </si>
   <si>
@@ -270,6 +244,9 @@
   </si>
   <si>
     <t>ZIP code of employeer group</t>
+  </si>
+  <si>
+    <t>List of months member was eligible (dfference between eff. and term. date)</t>
   </si>
 </sst>
 </file>
@@ -717,19 +694,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0588D786-E79F-4CD7-9DC2-8224410D79EB}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="20.453125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="20.44140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.26953125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="26.453125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="20.453125" style="2"/>
+    <col min="1" max="1" width="22.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.21875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="20.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -749,7 +726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -765,7 +742,7 @@
       </c>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -781,7 +758,7 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -799,7 +776,7 @@
       </c>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -819,7 +796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -839,7 +816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
@@ -857,7 +834,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -875,7 +852,7 @@
       </c>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>31</v>
       </c>
@@ -893,7 +870,7 @@
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
@@ -913,7 +890,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -929,7 +906,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
@@ -945,7 +922,7 @@
       </c>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>44</v>
       </c>
@@ -963,7 +940,7 @@
       </c>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>47</v>
       </c>
@@ -971,160 +948,142 @@
         <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="3" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+      <c r="E18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="D19" s="4"/>
       <c r="E19" s="4" t="s">
         <v>9</v>
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="4"/>
+        <v>72</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="E21" s="4" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
